--- a/260802.xlsx
+++ b/260802.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82BCCCA-AB53-4897-94F6-873CF078DCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D29C0E-4B03-44DF-9AA2-6F075B6BDBEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7630" yWindow="4110" windowWidth="15030" windowHeight="11170" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8400" yWindow="4110" windowWidth="15030" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -28,19 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>hinter ihm, Sie halten diese Fusion für richtig.
-Sind Sie sicher, dass Gabriel auch im schwierigen, heiklen Verfahren, um das es jetzt geht, alles richtiggemacht hat?
-Scholz: Ich kenne die Akten nicht, 
-Immerhin ist es ja so, zu erlauben aus politischen Erwägungen heraus
-Detjen: Ist das für die SPD auch eine Chance, mal wieder den Schulterschluss mit den Gewerkschaften im Kampf um Arbeitsplätze zu demonstrieren?
-Bundeskartellamt, Monopolkommission –, die eine andere Entscheidung empfohlen oder nahegelegt haben.
-Scholz: Er ist nicht der Erste, der das tut.
-Minister, die dieses Amt vor ihm hatten.
-Das könnte die Zeit sein, eine vorläufige Bilanz der Großen Koalition zu ziehen, mit der sich Ihre Partei, die SPD, am Anfang ja schwergetan hat.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Und die Zeit, in der sie immer vertröstet wurden, dass das nun mal so ist in der Globalisierung, dass man das nicht alles machen kann und wir kein Geld haben.
 Geers: Ist das jetzt gerade der Einblick gewesen in das, auf Angela Merkel zugeschnittenen Wahlkampf führen dürfte – den Sie dann mit SPD mit Sachthemen kontern werden?
@@ -57,6 +45,20 @@
 Das heißt, noch ist die Politik da nicht Ihren Wünschen gemäß.
 Aber natürlich ist die Politik involviert und , die halt von A nach B in die Welt gebracht werden wollen, aber nicht unbedingt sagen, das Auto muss mir gehören.</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hinter ihm, Sie halten diese Fusion</t>
+  </si>
+  <si>
+    <t>Ich kenne die Akten nicht, Immerhin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Gewerkschaften im Kampf </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zeit sein</t>
   </si>
 </sst>
 </file>
@@ -384,15 +386,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DFFAB53-C583-4AFF-8D70-834CE7204999}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -411,7 +428,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="378" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -430,7 +447,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="154" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
